--- a/ig/document/StructureDefinition-medcom-document-organization.xlsx
+++ b/ig/document/StructureDefinition-medcom-document-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T10:37:57+00:00</t>
+    <t>2026-03-10T10:54:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1888,7 +1888,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>85</v>
       </c>
@@ -2342,7 +2342,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>114</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>139</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>147</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>184</v>
       </c>
@@ -4054,7 +4054,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>215</v>
       </c>
@@ -4170,7 +4170,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>227</v>
       </c>
@@ -8178,7 +8178,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>326</v>
       </c>
@@ -9786,12 +9786,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN71">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/ig/document/StructureDefinition-medcom-document-organization.xlsx
+++ b/ig/document/StructureDefinition-medcom-document-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T10:54:08+00:00</t>
+    <t>2026-04-29T08:07:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
